--- a/data/trans_bre/P68-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P68-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 10,5</t>
+          <t>-11,65; 10,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 15,63</t>
+          <t>-11,81; 15,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,92; 11,75</t>
+          <t>-15,96; 10,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 5,1</t>
+          <t>-7,89; 5,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-37,78; 50,67</t>
+          <t>-39,19; 51,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-31,74; 58,22</t>
+          <t>-31,25; 59,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-31,15; 34,0</t>
+          <t>-33,23; 29,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-52,1; 62,76</t>
+          <t>-49,29; 61,8</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 9,06</t>
+          <t>-10,95; 8,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 8,54</t>
+          <t>-15,19; 6,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-23,17; 1,34</t>
+          <t>-22,42; 1,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 17,29</t>
+          <t>-1,94; 17,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,2; 38,26</t>
+          <t>-37,88; 35,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-41,6; 34,36</t>
+          <t>-40,99; 21,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-44,65; 2,16</t>
+          <t>-42,18; 4,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 120,56</t>
+          <t>-7,62; 116,65</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 12,81</t>
+          <t>-7,26; 13,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 16,41</t>
+          <t>-6,12; 16,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 8,71</t>
+          <t>-12,83; 7,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 15,42</t>
+          <t>-5,74; 15,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-32,45; 76,0</t>
+          <t>-30,87; 78,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-31,65; 120,18</t>
+          <t>-28,76; 119,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-59,6; 66,13</t>
+          <t>-58,39; 58,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-16,25; 55,96</t>
+          <t>-15,82; 59,71</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,7; -0,85</t>
+          <t>-17,23; -0,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,63; 9,19</t>
+          <t>-17,67; 8,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 22,98</t>
+          <t>-5,82; 23,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,64; 32,0</t>
+          <t>-13,65; 32,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-58,78; -1,77</t>
+          <t>-59,3; -0,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,28; 35,92</t>
+          <t>-45,07; 28,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,7; 95,47</t>
+          <t>-17,66; 106,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-52,04; 169,68</t>
+          <t>-49,2; 160,75</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,42; 6,39</t>
+          <t>-18,67; 6,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 15,73</t>
+          <t>-13,0; 16,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 3,88</t>
+          <t>-20,93; 4,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 2,14</t>
+          <t>-12,25; 1,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-74,81; 41,57</t>
+          <t>-75,0; 50,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-53,57; 114,47</t>
+          <t>-52,03; 129,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-79,42; 41,84</t>
+          <t>-80,41; 45,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-61,36; 25,45</t>
+          <t>-61,69; 12,41</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-20,6; 1,07</t>
+          <t>-20,11; 1,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-24,18; 5,05</t>
+          <t>-24,28; 5,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-22,02; -0,63</t>
+          <t>-21,61; -0,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,83; 22,0</t>
+          <t>1,19; 22,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-65,66; 4,93</t>
+          <t>-64,32; 6,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-58,06; 16,44</t>
+          <t>-58,38; 19,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-82,1; 4,97</t>
+          <t>-84,65; 1,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,48; 117,09</t>
+          <t>3,99; 128,32</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 5,84</t>
+          <t>-10,18; 6,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 14,19</t>
+          <t>-2,15; 13,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 4,43</t>
+          <t>-8,96; 5,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 8,71</t>
+          <t>-6,36; 7,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-34,49; 24,16</t>
+          <t>-34,62; 28,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 84,59</t>
+          <t>-10,77; 85,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-35,31; 23,13</t>
+          <t>-35,95; 27,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-20,67; 47,27</t>
+          <t>-23,46; 39,58</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 4,04</t>
+          <t>-9,51; 3,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 4,94</t>
+          <t>-6,54; 5,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 2,44</t>
+          <t>-7,93; 2,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,41; 22,4</t>
+          <t>4,11; 21,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,06; 18,91</t>
+          <t>-35,92; 17,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-43,15; 48,7</t>
+          <t>-43,53; 50,48</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-58,44; 30,58</t>
+          <t>-55,99; 27,68</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,82; 541,31</t>
+          <t>25,4; 613,89</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 0,33</t>
+          <t>-6,42; -0,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 2,94</t>
+          <t>-4,03; 2,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,44; -0,46</t>
+          <t>-7,25; -0,5</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,1; 14,28</t>
+          <t>2,06; 14,29</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 1,28</t>
+          <t>-24,45; -0,08</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-17,41; 12,92</t>
+          <t>-15,99; 13,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-27,73; -1,23</t>
+          <t>-27,42; -1,85</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10,36; 105,51</t>
+          <t>10,64; 109,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P68-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P68-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,48</t>
+          <t>-2,35</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-11,93%</t>
+          <t>-18,13%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 10,44</t>
+          <t>-10,82; 11,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 15,88</t>
+          <t>-10,46; 16,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,96; 10,62</t>
+          <t>-15,65; 11,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 5,4</t>
+          <t>-8,29; 3,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-39,19; 51,31</t>
+          <t>-36,86; 52,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-31,25; 59,4</t>
+          <t>-28,12; 59,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-33,23; 29,28</t>
+          <t>-31,94; 29,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-49,29; 61,8</t>
+          <t>-50,51; 38,3</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,21</t>
+          <t>7,59</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 8,1</t>
+          <t>-11,38; 7,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 6,17</t>
+          <t>-16,43; 7,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,42; 1,92</t>
+          <t>-22,39; 1,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 17,83</t>
+          <t>-1,22; 15,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,88; 35,78</t>
+          <t>-39,17; 34,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,99; 21,8</t>
+          <t>-42,8; 26,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,18; 4,5</t>
+          <t>-43,81; 2,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 116,65</t>
+          <t>-5,36; 99,37</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,28</t>
+          <t>4,61</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 13,37</t>
+          <t>-7,62; 13,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 16,11</t>
+          <t>-6,39; 14,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 7,72</t>
+          <t>-11,57; 8,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 15,45</t>
+          <t>-5,28; 15,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-30,87; 78,5</t>
+          <t>-32,11; 85,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-28,76; 119,7</t>
+          <t>-32,76; 106,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-58,39; 58,32</t>
+          <t>-54,37; 73,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 59,71</t>
+          <t>-13,52; 52,73</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,27</t>
+          <t>4,05</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,23; -0,42</t>
+          <t>-17,41; -0,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 8,07</t>
+          <t>-16,67; 7,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 23,43</t>
+          <t>-5,13; 23,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,65; 32,65</t>
+          <t>-6,83; 14,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-59,3; -0,06</t>
+          <t>-59,08; -0,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,07; 28,68</t>
+          <t>-44,19; 30,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,66; 106,46</t>
+          <t>-16,3; 103,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-49,2; 160,75</t>
+          <t>-21,48; 76,16</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-5,15</t>
+          <t>-4,37</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-33,14%</t>
+          <t>-27,5%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,67; 6,9</t>
+          <t>-17,87; 7,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 16,4</t>
+          <t>-12,93; 15,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,93; 4,43</t>
+          <t>-19,18; 4,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 1,4</t>
+          <t>-12,26; 2,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-75,0; 50,94</t>
+          <t>-70,91; 53,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-52,03; 129,78</t>
+          <t>-53,85; 119,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-80,41; 45,48</t>
+          <t>-79,14; 50,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-61,69; 12,41</t>
+          <t>-57,96; 19,52</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11,43</t>
+          <t>10,72</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>44,15%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 1,27</t>
+          <t>-20,12; 0,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 5,94</t>
+          <t>-24,41; 4,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-21,61; -0,32</t>
+          <t>-21,47; 0,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,19; 22,98</t>
+          <t>-1,09; 20,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-64,32; 6,83</t>
+          <t>-62,46; 4,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-58,38; 19,93</t>
+          <t>-56,76; 15,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-84,65; 1,84</t>
+          <t>-82,91; 4,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,99; 128,32</t>
+          <t>-4,23; 104,94</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,22</t>
+          <t>0,29</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 6,64</t>
+          <t>-10,45; 6,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 13,88</t>
+          <t>-2,8; 13,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 5,06</t>
+          <t>-8,73; 4,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 7,37</t>
+          <t>-6,6; 6,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-34,62; 28,7</t>
+          <t>-35,96; 25,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 85,02</t>
+          <t>-11,03; 79,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-35,95; 27,8</t>
+          <t>-35,82; 22,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-23,46; 39,58</t>
+          <t>-25,13; 32,14</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11,2</t>
+          <t>3,81</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>124,02%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 3,65</t>
+          <t>-9,01; 3,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 5,17</t>
+          <t>-6,55; 4,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 2,45</t>
+          <t>-8,01; 2,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,11; 21,75</t>
+          <t>-1,76; 9,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,92; 17,14</t>
+          <t>-34,79; 16,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-43,53; 50,48</t>
+          <t>-43,49; 45,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-55,99; 27,68</t>
+          <t>-55,83; 33,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>25,4; 613,89</t>
+          <t>-9,53; 78,74</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7,02</t>
+          <t>2,92</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,42; -0,09</t>
+          <t>-6,81; -0,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 2,82</t>
+          <t>-3,79; 3,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,25; -0,5</t>
+          <t>-7,7; -0,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,06; 14,29</t>
+          <t>-0,01; 5,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-24,45; -0,08</t>
+          <t>-26,05; -1,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-15,99; 13,2</t>
+          <t>-15,53; 15,64</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-27,42; -1,85</t>
+          <t>-28,19; 0,21</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10,64; 109,12</t>
+          <t>-0,02; 30,33</t>
         </is>
       </c>
     </row>
